--- a/templates/Directory-2.xlsx
+++ b/templates/Directory-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joseph\Downloads\_sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA41D378-0B44-4647-9478-203DE033E1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A6B2B5-BD6E-43EE-A005-E3567AB717BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
   <si>
     <t>Directory of Participants</t>
   </si>
@@ -125,13 +125,7 @@
     <t> PREPARED BY:</t>
   </si>
   <si>
-    <t>Training Assistant</t>
-  </si>
-  <si>
     <t>NOTED BY:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traiing Manager </t>
   </si>
   <si>
     <t>LIST OF TRAININGS CONDUCTED</t>
@@ -215,13 +209,10 @@
     <t>PETROSPHERE INCORPORATED</t>
   </si>
   <si>
-    <t>MICHELLE M. SACLET</t>
+    <t>Operations Manager</t>
   </si>
   <si>
-    <t>JEFFREY C. GEALON</t>
-  </si>
-  <si>
-    <t>Michelle M. Saclet</t>
+    <t>Training Facilitator</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1363,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" s="82"/>
       <c r="E9" s="82"/>
@@ -2150,14 +2141,12 @@
       <c r="B44" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="57" t="s">
-        <v>60</v>
-      </c>
+      <c r="C44" s="57"/>
     </row>
     <row r="45" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B45" s="52"/>
       <c r="C45" s="41" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2166,15 +2155,13 @@
     </row>
     <row r="47" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="57" t="s">
-        <v>61</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C47" s="57"/>
     </row>
     <row r="48" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C48" s="41" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3169,7 +3156,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="96" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B1" s="96"/>
       <c r="C1" s="96"/>
@@ -3216,7 +3203,7 @@
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="100" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" s="101"/>
       <c r="C4" s="101"/>
@@ -3264,7 +3251,7 @@
     <row r="7" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" s="102" t="s">
         <v>2</v>
@@ -3282,11 +3269,9 @@
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="102" t="s">
-        <v>62</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="C9" s="102"/>
       <c r="D9" s="102"/>
       <c r="E9" s="102"/>
       <c r="F9" s="102"/>
@@ -3300,7 +3285,7 @@
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="40" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C10" s="103"/>
       <c r="D10" s="103"/>
@@ -3328,28 +3313,28 @@
         <v>6</v>
       </c>
       <c r="B12" s="97" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="97" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="97" t="s">
+      <c r="E12" s="99" t="s">
         <v>38</v>
-      </c>
-      <c r="D12" s="97" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="99" t="s">
-        <v>40</v>
       </c>
       <c r="F12" s="98"/>
       <c r="G12" s="98"/>
       <c r="H12" s="98"/>
       <c r="I12" s="97" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J12" s="98"/>
       <c r="K12" s="98"/>
       <c r="L12" s="98"/>
       <c r="M12" s="99" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="31" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3358,10 +3343,10 @@
       <c r="C13" s="98"/>
       <c r="D13" s="98"/>
       <c r="E13" s="32" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G13" s="33" t="s">
         <v>27</v>
@@ -3370,16 +3355,16 @@
         <v>14</v>
       </c>
       <c r="I13" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="J13" s="33" t="s">
+      <c r="L13" s="33" t="s">
         <v>46</v>
-      </c>
-      <c r="K13" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="L13" s="33" t="s">
-        <v>48</v>
       </c>
       <c r="M13" s="98"/>
     </row>
@@ -5212,7 +5197,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="104" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B1" s="101"/>
       <c r="C1" s="101"/>
@@ -5271,7 +5256,7 @@
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C5" s="105"/>
       <c r="D5" s="106"/>
@@ -5279,7 +5264,7 @@
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" s="105"/>
       <c r="D6" s="106"/>
@@ -5287,7 +5272,7 @@
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" s="105"/>
       <c r="D7" s="106"/>
@@ -5299,16 +5284,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>39</v>
-      </c>
       <c r="D9" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>10</v>
@@ -5317,31 +5302,31 @@
         <v>12</v>
       </c>
       <c r="H9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="K9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>21</v>
       </c>
       <c r="N9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P9" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>57</v>
       </c>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
